--- a/reference_data/Y4_B2526_General_&_Special_Internal_1_A2_reference_data.xlsx
+++ b/reference_data/Y4_B2526_General_&_Special_Internal_1_A2_reference_data.xlsx
@@ -6410,7 +6410,7 @@
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>A2C</t>
+          <t>A2D</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
